--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-12).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-176</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 1.699.734,09</t>
-  </si>
-  <si>
-    <t>R$ 9.138,36
-R$ 9.325,33</t>
+177</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 1.710.867,53</t>
+  </si>
+  <si>
+    <t>R$ 9.149,02
+R$ 9.335,55</t>
   </si>
   <si>
     <t>(5.7%)
 (4.0%)</t>
   </si>
   <si>
-    <t>96.7</t>
-  </si>
-  <si>
-    <t>(9.1%)</t>
-  </si>
-  <si>
-    <t>33.1%</t>
-  </si>
-  <si>
-    <t>(11.4%)</t>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>(9.2%)</t>
+  </si>
+  <si>
+    <t>33.2%</t>
+  </si>
+  <si>
+    <t>(11.3%)</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>27.8</t>
   </si>
   <si>
-    <t>63.0%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
+    <t>62.8%</t>
+  </si>
+  <si>
+    <t>11.5%</t>
   </si>
   <si>
     <t>6.0</t>
@@ -962,19 +962,19 @@
     <t>6.7</t>
   </si>
   <si>
-    <t>12.8</t>
+    <t>12.7</t>
   </si>
   <si>
     <t>19.4</t>
   </si>
   <si>
-    <t>68.3%</t>
-  </si>
-  <si>
-    <t>-R$ 49.088,98</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>68.4%</t>
+  </si>
+  <si>
+    <t>-R$ 49.422,18</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8722,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8758,27 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.047526815855617799</v>
+      </c>
+      <c r="R58" s="7">
+        <v>125</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.10071942446043169</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.40038817292768447</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.029430050370774886</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.012320989739020466</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.00052679136008277759</v>
+      </c>
+      <c r="X58" s="8">
+        <v>25.836425773195877</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.46391752577319589</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.010309278350515464</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.5377952755905513</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.3771474226804123</v>
+      </c>
       <c r="AC58" s="8">
         <v>11.251636</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>16.395659375000001</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.83505154639175261</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-333.19999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15407,7 +15441,9 @@
       <c r="AB111" s="8">
         <v>2.8539235294117646</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.980391</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.913723529411765</v>
       </c>
@@ -15419,7 +15455,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15772,7 +15808,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16909,7 +16945,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17302,7 +17338,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18471,7 +18507,7 @@
         <v>-258.80000000000001</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20789,7 +20825,7 @@
         <v>-2724.3600000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22001,7 +22037,7 @@
         <v>-1004.66</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24079,7 +24115,9 @@
       <c r="AB179" s="8">
         <v>1.8164285714285715</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.9235699999999998</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.88381</v>
       </c>
@@ -28164,7 +28202,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
